--- a/dokumanlar/hazir-olcekler/4-sinif/matematik/4-sinif-matematik-kazanim-olcegi.xlsx
+++ b/dokumanlar/hazir-olcekler/4-sinif/matematik/4-sinif-matematik-kazanim-olcegi.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Ölçek" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Ölçek!$A$1:$AG$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Ölçek!$A$1:$AJ$48</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t xml:space="preserve">📝 BİLGİLERİ DOLDURUNUZ</t>
   </si>
@@ -48,13 +48,13 @@
     <t xml:space="preserve">Ders</t>
   </si>
   <si>
+    <t xml:space="preserve">Matematik</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sınıf Öğretmeni</t>
   </si>
   <si>
     <t xml:space="preserve">Okul Müdürü</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ℹ️ ÖRNEK: Okul Adı: ABC İLKOKULU  •  Sınıf: 4/A  •  Dönem: 1. DÖNEM  •  Ders: MATEMATİK</t>
   </si>
   <si>
     <t xml:space="preserve">📋 SİSTEMDEN ÖĞRENCİ LİSTESİNİ BURAYA YAPIŞTIRIN</t>
@@ -93,91 +93,100 @@
     <t xml:space="preserve">ADI VE SOYADI</t>
   </si>
   <si>
-    <t xml:space="preserve">4, 5 ve 6 basamaklı doğal sayıları okur ve yazar.</t>
+    <t xml:space="preserve">4, 5 ve 6 basamaklı doğal sayıları okur ve yazar</t>
   </si>
   <si>
-    <t xml:space="preserve">4, 5 ve 6 basamaklı sayıların basamak adlarını ve değerlerini belirler.</t>
+    <t xml:space="preserve">4, 5 ve 6 basamaklı doğal sayıların bölüklerini ve basamaklarını, basamaklarındaki rakamların basamak değerlerini belirler ve çözümler</t>
   </si>
   <si>
-    <t xml:space="preserve">10 000'e kadar yüzer ve biner ritmik sayar.</t>
+    <t xml:space="preserve">En çok altı basamaklı doğal sayıları büyük/küçük sembolü kullanarak sıralar</t>
   </si>
   <si>
-    <t xml:space="preserve">Doğal sayıları en yakın onluğa veya yüzlüğe yuvarlar.</t>
+    <t xml:space="preserve">En çok dört basamaklı doğal sayılarla toplama işlemini yapar</t>
   </si>
   <si>
-    <t xml:space="preserve">En çok altı basamaklı doğal sayıları büyüktür/küçüktür sembolü ile karşılaştırır.</t>
+    <t xml:space="preserve">En çok dört basamaklı doğal sayıları 100’ün katlarıyla zihinden toplar</t>
   </si>
   <si>
-    <t xml:space="preserve">Belli bir kurala göre artan veya azalan sayı örüntüleri oluşturur.</t>
+    <t xml:space="preserve">Üç basamaklı doğal sayılardan 10’un katı olan iki basamaklı doğal sayıları ve 100’ün katı olan üç basamaklı doğal sayıları zihinden çıkarır</t>
   </si>
   <si>
-    <t xml:space="preserve">En çok dört basamaklı doğal sayılarla toplama işlemi yapar.</t>
+    <t xml:space="preserve">Doğal sayılarla toplama ve çıkarma işlemini gerektiren problemleri çözer</t>
   </si>
   <si>
-    <t xml:space="preserve">İki doğal sayının toplamını tahmin eder ve sonucuyla karşılaştırır.</t>
+    <t xml:space="preserve">Üç doğal sayı ile yapılan çarpma işleminde sayıların birbirleriyle çarpılma sırasının değişmesinin, sonucu değiştirmediğini gösterir</t>
   </si>
   <si>
-    <t xml:space="preserve">En çok dört basamaklı doğal sayılarla çıkarma işlemi yapar.</t>
+    <t xml:space="preserve">En çok üç basamaklı doğal sayıları 10, 100 ve 1000 ile zihinden çarpar</t>
   </si>
   <si>
-    <t xml:space="preserve">Toplama ve çıkarma işlemleri gerektiren problemleri çözer.</t>
+    <t xml:space="preserve">Doğal sayılarla çarpma işlemini gerektiren problemleri çözer</t>
   </si>
   <si>
-    <t xml:space="preserve">Üç basamaklı doğal sayıları bir basamaklı sayılarla çarpar.</t>
+    <t xml:space="preserve">Son üç basamağı sıfır olan en çok beş basamaklı doğal sayıları 10, 100 ve 1000’e zihinden böler</t>
   </si>
   <si>
-    <t xml:space="preserve">İki basamaklı doğal sayıları iki basamaklı sayılarla çarpar.</t>
+    <t xml:space="preserve">Çarpma ve bölme arasındaki ilişkiyi fark eder</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir doğal sayıyı 10, 100 ve 1000 ile pratik yoldan çarpar.</t>
+    <t xml:space="preserve">Aralarında eşitlik durumu olan iki matematiksel ifadeden birinde verilmeyen değeri belirler ve eşitliğin sağlandığını açıklar</t>
   </si>
   <si>
-    <t xml:space="preserve">Üç basamaklı doğal sayıları bir basamaklı sayılara böler.</t>
+    <t xml:space="preserve">Basit, bileşik ve tam sayılı kesri tanır ve modellerle gösterir</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir doğal sayıyı 10, 100 ve 1000'e pratik yoldan böler.</t>
+    <t xml:space="preserve">Paydaları eşit olan en çok üç kesri karşılaştırır</t>
   </si>
   <si>
-    <t xml:space="preserve">Çarpma ve bölme işlemleri gerektiren problemleri çözer.</t>
+    <t xml:space="preserve">Kesirlerle toplama ve çıkarma işlemlerini gerektiren problemleri çözer</t>
   </si>
   <si>
-    <t xml:space="preserve">Birim kesirleri, basit kesirleri ve bileşik kesirleri tanır.</t>
+    <t xml:space="preserve">Kare ve dikdörtgenin kenar özelliklerini belirler</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir bütünü eşit parçalara ayırır ve kesir olarak ifade eder.</t>
+    <t xml:space="preserve">Açınımı verilen küpü oluşturur</t>
   </si>
   <si>
-    <t xml:space="preserve">Paydaları eşit kesirleri karşılaştırır.</t>
+    <t xml:space="preserve">Ayna simetrisini, geometrik şekiller ve modeller üzerinde açıklayarak simetri doğrusunu çizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Standart uzunluk ölçü birimlerini açıklar ve birbirine dönüştürür.</t>
+    <t xml:space="preserve">Açıyı oluşturan ışınları ve köşeyi belirler, açıyı isimlendirir ve sembolle gösterir</t>
   </si>
   <si>
-    <t xml:space="preserve">Uzunluk ölçü birimleriyle ilgili problemleri çözer.</t>
+    <t xml:space="preserve">Açıları standart açı ölçme araçlarıyla ölçerek dar, dik, geniş ve doğru açı olarak belirler</t>
   </si>
   <si>
-    <t xml:space="preserve">Standart zaman ölçü birimlerini açıklar.</t>
+    <t xml:space="preserve">Standart uzunluk ölçme birimlerinden milimetrenin kullanım alanlarını belirtir</t>
   </si>
   <si>
-    <t xml:space="preserve">Sıvıların ölçülmesinde kullanılan litre ve mililitre birimlerini açıklar.</t>
+    <t xml:space="preserve">Doğrudan ölçebileceği bir uzunluğu en uygun uzunluk ölçme birimiyle tahmin eder ve tahminini ölçme yaparak kontrol eder</t>
   </si>
   <si>
-    <t xml:space="preserve">Ağırlık (kütle) ölçü birimleriyle (kg, g) ilgili problemleri çözer.</t>
+    <t xml:space="preserve">Aynı çevre uzunluğuna sahip farklı geometrik şekiller oluşturur</t>
   </si>
   <si>
-    <t xml:space="preserve">Açıyı tanır ve standart olmayan birimlerle ölçer.</t>
+    <t xml:space="preserve">Şekillerin alanlarının, bu alanı kaplayan birim karelerin sayısı olduğunu belirler</t>
   </si>
   <si>
-    <t xml:space="preserve">Açıları çeşitlerine göre (dar, dik, geniş) ayırt eder.</t>
+    <t xml:space="preserve">Zaman ölçme birimleri arasındaki ilişkiyi açıklar</t>
   </si>
   <si>
-    <t xml:space="preserve">Üçgen, kare ve dikdörtgenin köşe ve kenar özelliklerini belirler.</t>
+    <t xml:space="preserve">Yarım ve çeyrek kilogramı gram cinsinden ifade eder</t>
   </si>
   <si>
-    <t xml:space="preserve">Karenin ve dikdörtgenin çevresini hesaplar.</t>
+    <t xml:space="preserve">Ton ve miligramın kullanıldığı yerleri belirler</t>
   </si>
   <si>
-    <t xml:space="preserve">Verileri tablo ve sütun grafiği ile gösterir, yorumlar.</t>
+    <t xml:space="preserve">Mililitrenin kullanıldığı yerleri açıklar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litre ve mililitreyi miktar belirtmek için bir arada kullanır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litre ve mililitre ile ilgili problemleri çözer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sütun grafiğini oluşturur</t>
   </si>
   <si>
     <t xml:space="preserve">ORTALAMA</t>
@@ -753,7 +762,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
@@ -800,31 +809,26 @@
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1334,14 +1338,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="3" style="0" width="3.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="3" style="0" width="3.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1381,11 +1385,14 @@
       <c r="AE1" s="11"/>
       <c r="AF1" s="11"/>
       <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="11"/>
+      <c r="AJ1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="str">
         <f aca="false">Bilgiler!B6&amp;" SINIFI "&amp;Bilgiler!B7&amp;" "&amp;Bilgiler!B8&amp;" DERSİ KAZANIM DEĞERLENDİRME ÖLÇEĞİ"</f>
-        <v> SINIFI   DERSİ KAZANIM DEĞERLENDİRME ÖLÇEĞİ</v>
+        <v> SINIFI  Matematik DERSİ KAZANIM DEĞERLENDİRME ÖLÇEĞİ</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1419,8 +1426,11 @@
       <c r="AE2" s="11"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
-    </row>
-    <row r="4" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>13</v>
       </c>
@@ -1514,11 +1524,20 @@
       <c r="AE4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" s="12" t="s">
+      <c r="AF4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AG4" s="12" t="s">
+      <c r="AG4" s="13" t="s">
         <v>52</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1531,126 +1550,138 @@
         <v/>
       </c>
       <c r="C5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE5" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",IF(AG5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AG5=""),"",ROUND(AVERAGE(C5:AE5),2))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH5" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",IF(AJ5="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ5="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ5="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ5="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI5" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B6="",AJ5=""),"",ROUND(AVERAGE(C5:AH5),2))</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G6="","",IF(UPPER(TRIM('Öğrenci Listesi'!G6))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G6))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G6))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G6))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G6))))),"")</f>
         <v/>
       </c>
@@ -1665,126 +1696,138 @@
         <v/>
       </c>
       <c r="C6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE6" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",IF(AG6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AG6=""),"",ROUND(AVERAGE(C6:AE6),2))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH6" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",IF(AJ6="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ6="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ6="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ6="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI6" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B7="",AJ6=""),"",ROUND(AVERAGE(C6:AH6),2))</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G7="","",IF(UPPER(TRIM('Öğrenci Listesi'!G7))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G7))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G7))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G7))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G7))))),"")</f>
         <v/>
       </c>
@@ -1799,126 +1842,138 @@
         <v/>
       </c>
       <c r="C7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE7" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",IF(AG7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AG7=""),"",ROUND(AVERAGE(C7:AE7),2))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",IF(AJ7="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ7="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ7="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ7="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B8="",AJ7=""),"",ROUND(AVERAGE(C7:AH7),2))</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G8="","",IF(UPPER(TRIM('Öğrenci Listesi'!G8))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G8))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G8))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G8))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G8))))),"")</f>
         <v/>
       </c>
@@ -1933,126 +1988,138 @@
         <v/>
       </c>
       <c r="C8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE8" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",IF(AG8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AG8=""),"",ROUND(AVERAGE(C8:AE8),2))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",IF(AJ8="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ8="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ8="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ8="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B9="",AJ8=""),"",ROUND(AVERAGE(C8:AH8),2))</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G9="","",IF(UPPER(TRIM('Öğrenci Listesi'!G9))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G9))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G9))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G9))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G9))))),"")</f>
         <v/>
       </c>
@@ -2067,126 +2134,138 @@
         <v/>
       </c>
       <c r="C9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE9" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",IF(AG9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AG9=""),"",ROUND(AVERAGE(C9:AE9),2))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",IF(AJ9="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ9="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ9="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ9="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B10="",AJ9=""),"",ROUND(AVERAGE(C9:AH9),2))</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G10="","",IF(UPPER(TRIM('Öğrenci Listesi'!G10))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G10))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G10))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G10))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G10))))),"")</f>
         <v/>
       </c>
@@ -2201,126 +2280,138 @@
         <v/>
       </c>
       <c r="C10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE10" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",IF(AG10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF10" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AG10=""),"",ROUND(AVERAGE(C10:AE10),2))</f>
-        <v/>
-      </c>
-      <c r="AG10" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",IF(AJ10="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ10="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ10="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ10="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B11="",AJ10=""),"",ROUND(AVERAGE(C10:AH10),2))</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G11="","",IF(UPPER(TRIM('Öğrenci Listesi'!G11))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G11))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G11))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G11))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G11))))),"")</f>
         <v/>
       </c>
@@ -2335,126 +2426,138 @@
         <v/>
       </c>
       <c r="C11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE11" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",IF(AG11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF11" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AG11=""),"",ROUND(AVERAGE(C11:AE11),2))</f>
-        <v/>
-      </c>
-      <c r="AG11" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",IF(AJ11="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ11="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ11="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ11="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B12="",AJ11=""),"",ROUND(AVERAGE(C11:AH11),2))</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G12="","",IF(UPPER(TRIM('Öğrenci Listesi'!G12))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G12))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G12))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G12))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G12))))),"")</f>
         <v/>
       </c>
@@ -2469,126 +2572,138 @@
         <v/>
       </c>
       <c r="C12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE12" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",IF(AG12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF12" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AG12=""),"",ROUND(AVERAGE(C12:AE12),2))</f>
-        <v/>
-      </c>
-      <c r="AG12" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",IF(AJ12="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ12="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ12="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ12="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B13="",AJ12=""),"",ROUND(AVERAGE(C12:AH12),2))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G13="","",IF(UPPER(TRIM('Öğrenci Listesi'!G13))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G13))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G13))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G13))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G13))))),"")</f>
         <v/>
       </c>
@@ -2603,126 +2718,138 @@
         <v/>
       </c>
       <c r="C13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE13" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",IF(AG13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AG13=""),"",ROUND(AVERAGE(C13:AE13),2))</f>
-        <v/>
-      </c>
-      <c r="AG13" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",IF(AJ13="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ13="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ13="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ13="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B14="",AJ13=""),"",ROUND(AVERAGE(C13:AH13),2))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G14="","",IF(UPPER(TRIM('Öğrenci Listesi'!G14))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G14))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G14))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G14))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G14))))),"")</f>
         <v/>
       </c>
@@ -2737,126 +2864,138 @@
         <v/>
       </c>
       <c r="C14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE14" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",IF(AG14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF14" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AG14=""),"",ROUND(AVERAGE(C14:AE14),2))</f>
-        <v/>
-      </c>
-      <c r="AG14" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",IF(AJ14="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ14="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ14="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ14="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B15="",AJ14=""),"",ROUND(AVERAGE(C14:AH14),2))</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G15="","",IF(UPPER(TRIM('Öğrenci Listesi'!G15))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G15))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G15))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G15))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G15))))),"")</f>
         <v/>
       </c>
@@ -2871,126 +3010,138 @@
         <v/>
       </c>
       <c r="C15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE15" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",IF(AG15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF15" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AG15=""),"",ROUND(AVERAGE(C15:AE15),2))</f>
-        <v/>
-      </c>
-      <c r="AG15" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",IF(AJ15="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ15="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ15="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ15="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B16="",AJ15=""),"",ROUND(AVERAGE(C15:AH15),2))</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G16="","",IF(UPPER(TRIM('Öğrenci Listesi'!G16))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G16))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G16))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G16))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G16))))),"")</f>
         <v/>
       </c>
@@ -3005,126 +3156,138 @@
         <v/>
       </c>
       <c r="C16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE16" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",IF(AG16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF16" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AG16=""),"",ROUND(AVERAGE(C16:AE16),2))</f>
-        <v/>
-      </c>
-      <c r="AG16" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",IF(AJ16="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ16="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ16="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ16="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B17="",AJ16=""),"",ROUND(AVERAGE(C16:AH16),2))</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G17="","",IF(UPPER(TRIM('Öğrenci Listesi'!G17))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G17))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G17))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G17))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G17))))),"")</f>
         <v/>
       </c>
@@ -3139,126 +3302,138 @@
         <v/>
       </c>
       <c r="C17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE17" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",IF(AG17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF17" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AG17=""),"",ROUND(AVERAGE(C17:AE17),2))</f>
-        <v/>
-      </c>
-      <c r="AG17" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",IF(AJ17="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ17="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ17="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ17="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B18="",AJ17=""),"",ROUND(AVERAGE(C17:AH17),2))</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G18="","",IF(UPPER(TRIM('Öğrenci Listesi'!G18))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G18))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G18))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G18))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G18))))),"")</f>
         <v/>
       </c>
@@ -3273,126 +3448,138 @@
         <v/>
       </c>
       <c r="C18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE18" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",IF(AG18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF18" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AG18=""),"",ROUND(AVERAGE(C18:AE18),2))</f>
-        <v/>
-      </c>
-      <c r="AG18" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",IF(AJ18="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ18="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ18="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ18="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B19="",AJ18=""),"",ROUND(AVERAGE(C18:AH18),2))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G19="","",IF(UPPER(TRIM('Öğrenci Listesi'!G19))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G19))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G19))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G19))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G19))))),"")</f>
         <v/>
       </c>
@@ -3407,126 +3594,138 @@
         <v/>
       </c>
       <c r="C19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE19" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",IF(AG19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF19" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AG19=""),"",ROUND(AVERAGE(C19:AE19),2))</f>
-        <v/>
-      </c>
-      <c r="AG19" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",IF(AJ19="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ19="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ19="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ19="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B20="",AJ19=""),"",ROUND(AVERAGE(C19:AH19),2))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G20="","",IF(UPPER(TRIM('Öğrenci Listesi'!G20))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G20))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G20))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G20))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G20))))),"")</f>
         <v/>
       </c>
@@ -3541,126 +3740,138 @@
         <v/>
       </c>
       <c r="C20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE20" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",IF(AG20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF20" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AG20=""),"",ROUND(AVERAGE(C20:AE20),2))</f>
-        <v/>
-      </c>
-      <c r="AG20" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",IF(AJ20="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ20="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ20="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ20="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B21="",AJ20=""),"",ROUND(AVERAGE(C20:AH20),2))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G21="","",IF(UPPER(TRIM('Öğrenci Listesi'!G21))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G21))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G21))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G21))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G21))))),"")</f>
         <v/>
       </c>
@@ -3675,126 +3886,138 @@
         <v/>
       </c>
       <c r="C21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE21" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",IF(AG21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AG21=""),"",ROUND(AVERAGE(C21:AE21),2))</f>
-        <v/>
-      </c>
-      <c r="AG21" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",IF(AJ21="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ21="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ21="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ21="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B22="",AJ21=""),"",ROUND(AVERAGE(C21:AH21),2))</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G22="","",IF(UPPER(TRIM('Öğrenci Listesi'!G22))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G22))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G22))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G22))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G22))))),"")</f>
         <v/>
       </c>
@@ -3809,126 +4032,138 @@
         <v/>
       </c>
       <c r="C22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE22" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",IF(AG22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AG22=""),"",ROUND(AVERAGE(C22:AE22),2))</f>
-        <v/>
-      </c>
-      <c r="AG22" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",IF(AJ22="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ22="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ22="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ22="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B23="",AJ22=""),"",ROUND(AVERAGE(C22:AH22),2))</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G23="","",IF(UPPER(TRIM('Öğrenci Listesi'!G23))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G23))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G23))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G23))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G23))))),"")</f>
         <v/>
       </c>
@@ -3943,126 +4178,138 @@
         <v/>
       </c>
       <c r="C23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE23" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",IF(AG23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AG23=""),"",ROUND(AVERAGE(C23:AE23),2))</f>
-        <v/>
-      </c>
-      <c r="AG23" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",IF(AJ23="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ23="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ23="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ23="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B24="",AJ23=""),"",ROUND(AVERAGE(C23:AH23),2))</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G24="","",IF(UPPER(TRIM('Öğrenci Listesi'!G24))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G24))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G24))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G24))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G24))))),"")</f>
         <v/>
       </c>
@@ -4077,126 +4324,138 @@
         <v/>
       </c>
       <c r="C24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE24" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",IF(AG24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AG24=""),"",ROUND(AVERAGE(C24:AE24),2))</f>
-        <v/>
-      </c>
-      <c r="AG24" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",IF(AJ24="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ24="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ24="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ24="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B25="",AJ24=""),"",ROUND(AVERAGE(C24:AH24),2))</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G25="","",IF(UPPER(TRIM('Öğrenci Listesi'!G25))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G25))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G25))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G25))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G25))))),"")</f>
         <v/>
       </c>
@@ -4211,126 +4470,138 @@
         <v/>
       </c>
       <c r="C25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE25" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",IF(AG25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AG25=""),"",ROUND(AVERAGE(C25:AE25),2))</f>
-        <v/>
-      </c>
-      <c r="AG25" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",IF(AJ25="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ25="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ25="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ25="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B26="",AJ25=""),"",ROUND(AVERAGE(C25:AH25),2))</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G26="","",IF(UPPER(TRIM('Öğrenci Listesi'!G26))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G26))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G26))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G26))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G26))))),"")</f>
         <v/>
       </c>
@@ -4345,126 +4616,138 @@
         <v/>
       </c>
       <c r="C26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE26" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",IF(AG26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AG26=""),"",ROUND(AVERAGE(C26:AE26),2))</f>
-        <v/>
-      </c>
-      <c r="AG26" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",IF(AJ26="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ26="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ26="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ26="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B27="",AJ26=""),"",ROUND(AVERAGE(C26:AH26),2))</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G27="","",IF(UPPER(TRIM('Öğrenci Listesi'!G27))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G27))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G27))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G27))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G27))))),"")</f>
         <v/>
       </c>
@@ -4479,126 +4762,138 @@
         <v/>
       </c>
       <c r="C27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE27" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",IF(AG27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AG27=""),"",ROUND(AVERAGE(C27:AE27),2))</f>
-        <v/>
-      </c>
-      <c r="AG27" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",IF(AJ27="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ27="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ27="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ27="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B28="",AJ27=""),"",ROUND(AVERAGE(C27:AH27),2))</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G28="","",IF(UPPER(TRIM('Öğrenci Listesi'!G28))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G28))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G28))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G28))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G28))))),"")</f>
         <v/>
       </c>
@@ -4613,126 +4908,138 @@
         <v/>
       </c>
       <c r="C28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE28" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",IF(AG28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF28" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AG28=""),"",ROUND(AVERAGE(C28:AE28),2))</f>
-        <v/>
-      </c>
-      <c r="AG28" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",IF(AJ28="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ28="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ28="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ28="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B29="",AJ28=""),"",ROUND(AVERAGE(C28:AH28),2))</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G29="","",IF(UPPER(TRIM('Öğrenci Listesi'!G29))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G29))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G29))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G29))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G29))))),"")</f>
         <v/>
       </c>
@@ -4747,126 +5054,138 @@
         <v/>
       </c>
       <c r="C29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE29" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",IF(AG29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF29" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AG29=""),"",ROUND(AVERAGE(C29:AE29),2))</f>
-        <v/>
-      </c>
-      <c r="AG29" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH29" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",IF(AJ29="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ29="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ29="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ29="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI29" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B30="",AJ29=""),"",ROUND(AVERAGE(C29:AH29),2))</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G30="","",IF(UPPER(TRIM('Öğrenci Listesi'!G30))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G30))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G30))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G30))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G30))))),"")</f>
         <v/>
       </c>
@@ -4881,126 +5200,138 @@
         <v/>
       </c>
       <c r="C30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE30" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",IF(AG30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF30" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AG30=""),"",ROUND(AVERAGE(C30:AE30),2))</f>
-        <v/>
-      </c>
-      <c r="AG30" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH30" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",IF(AJ30="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ30="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ30="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ30="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI30" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B31="",AJ30=""),"",ROUND(AVERAGE(C30:AH30),2))</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G31="","",IF(UPPER(TRIM('Öğrenci Listesi'!G31))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G31))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G31))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G31))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G31))))),"")</f>
         <v/>
       </c>
@@ -5015,126 +5346,138 @@
         <v/>
       </c>
       <c r="C31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE31" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",IF(AG31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF31" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AG31=""),"",ROUND(AVERAGE(C31:AE31),2))</f>
-        <v/>
-      </c>
-      <c r="AG31" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH31" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",IF(AJ31="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ31="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ31="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ31="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI31" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B32="",AJ31=""),"",ROUND(AVERAGE(C31:AH31),2))</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G32="","",IF(UPPER(TRIM('Öğrenci Listesi'!G32))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G32))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G32))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G32))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G32))))),"")</f>
         <v/>
       </c>
@@ -5149,126 +5492,138 @@
         <v/>
       </c>
       <c r="C32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE32" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",IF(AG32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF32" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AG32=""),"",ROUND(AVERAGE(C32:AE32),2))</f>
-        <v/>
-      </c>
-      <c r="AG32" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH32" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",IF(AJ32="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ32="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ32="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ32="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI32" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B33="",AJ32=""),"",ROUND(AVERAGE(C32:AH32),2))</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G33="","",IF(UPPER(TRIM('Öğrenci Listesi'!G33))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G33))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G33))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G33))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G33))))),"")</f>
         <v/>
       </c>
@@ -5283,126 +5638,138 @@
         <v/>
       </c>
       <c r="C33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE33" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",IF(AG33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF33" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AG33=""),"",ROUND(AVERAGE(C33:AE33),2))</f>
-        <v/>
-      </c>
-      <c r="AG33" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH33" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",IF(AJ33="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ33="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ33="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ33="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI33" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B34="",AJ33=""),"",ROUND(AVERAGE(C33:AH33),2))</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G34="","",IF(UPPER(TRIM('Öğrenci Listesi'!G34))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G34))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G34))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G34))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G34))))),"")</f>
         <v/>
       </c>
@@ -5417,126 +5784,138 @@
         <v/>
       </c>
       <c r="C34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE34" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",IF(AG34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF34" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AG34=""),"",ROUND(AVERAGE(C34:AE34),2))</f>
-        <v/>
-      </c>
-      <c r="AG34" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH34" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",IF(AJ34="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ34="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ34="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ34="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI34" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B35="",AJ34=""),"",ROUND(AVERAGE(C34:AH34),2))</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G35="","",IF(UPPER(TRIM('Öğrenci Listesi'!G35))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G35))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G35))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G35))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G35))))),"")</f>
         <v/>
       </c>
@@ -5551,126 +5930,138 @@
         <v/>
       </c>
       <c r="C35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE35" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",IF(AG35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF35" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AG35=""),"",ROUND(AVERAGE(C35:AE35),2))</f>
-        <v/>
-      </c>
-      <c r="AG35" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH35" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",IF(AJ35="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ35="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ35="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ35="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI35" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B36="",AJ35=""),"",ROUND(AVERAGE(C35:AH35),2))</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G36="","",IF(UPPER(TRIM('Öğrenci Listesi'!G36))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G36))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G36))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G36))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G36))))),"")</f>
         <v/>
       </c>
@@ -5685,126 +6076,138 @@
         <v/>
       </c>
       <c r="C36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE36" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",IF(AG36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF36" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AG36=""),"",ROUND(AVERAGE(C36:AE36),2))</f>
-        <v/>
-      </c>
-      <c r="AG36" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH36" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",IF(AJ36="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ36="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ36="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ36="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI36" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B37="",AJ36=""),"",ROUND(AVERAGE(C36:AH36),2))</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G37="","",IF(UPPER(TRIM('Öğrenci Listesi'!G37))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G37))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G37))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G37))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G37))))),"")</f>
         <v/>
       </c>
@@ -5819,126 +6222,138 @@
         <v/>
       </c>
       <c r="C37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE37" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",IF(AG37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF37" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AG37=""),"",ROUND(AVERAGE(C37:AE37),2))</f>
-        <v/>
-      </c>
-      <c r="AG37" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH37" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",IF(AJ37="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ37="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ37="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ37="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI37" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B38="",AJ37=""),"",ROUND(AVERAGE(C37:AH37),2))</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G38="","",IF(UPPER(TRIM('Öğrenci Listesi'!G38))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G38))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G38))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G38))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G38))))),"")</f>
         <v/>
       </c>
@@ -5953,126 +6368,138 @@
         <v/>
       </c>
       <c r="C38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE38" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",IF(AG38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF38" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AG38=""),"",ROUND(AVERAGE(C38:AE38),2))</f>
-        <v/>
-      </c>
-      <c r="AG38" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF38" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG38" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH38" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",IF(AJ38="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ38="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ38="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ38="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI38" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B39="",AJ38=""),"",ROUND(AVERAGE(C38:AH38),2))</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G39="","",IF(UPPER(TRIM('Öğrenci Listesi'!G39))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G39))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G39))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G39))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G39))))),"")</f>
         <v/>
       </c>
@@ -6087,126 +6514,138 @@
         <v/>
       </c>
       <c r="C39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE39" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",IF(AG39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF39" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AG39=""),"",ROUND(AVERAGE(C39:AE39),2))</f>
-        <v/>
-      </c>
-      <c r="AG39" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF39" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG39" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH39" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",IF(AJ39="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ39="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ39="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ39="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI39" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B40="",AJ39=""),"",ROUND(AVERAGE(C39:AH39),2))</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G40="","",IF(UPPER(TRIM('Öğrenci Listesi'!G40))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G40))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G40))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G40))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G40))))),"")</f>
         <v/>
       </c>
@@ -6221,126 +6660,138 @@
         <v/>
       </c>
       <c r="C40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE40" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",IF(AG40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF40" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AG40=""),"",ROUND(AVERAGE(C40:AE40),2))</f>
-        <v/>
-      </c>
-      <c r="AG40" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF40" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG40" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH40" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",IF(AJ40="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ40="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ40="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ40="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI40" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B41="",AJ40=""),"",ROUND(AVERAGE(C40:AH40),2))</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G41="","",IF(UPPER(TRIM('Öğrenci Listesi'!G41))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G41))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G41))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G41))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G41))))),"")</f>
         <v/>
       </c>
@@ -6355,126 +6806,138 @@
         <v/>
       </c>
       <c r="C41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE41" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",IF(AG41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF41" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AG41=""),"",ROUND(AVERAGE(C41:AE41),2))</f>
-        <v/>
-      </c>
-      <c r="AG41" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF41" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG41" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH41" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",IF(AJ41="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ41="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ41="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ41="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI41" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B42="",AJ41=""),"",ROUND(AVERAGE(C41:AH41),2))</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G42="","",IF(UPPER(TRIM('Öğrenci Listesi'!G42))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G42))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G42))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G42))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G42))))),"")</f>
         <v/>
       </c>
@@ -6489,126 +6952,138 @@
         <v/>
       </c>
       <c r="C42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE42" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",IF(AG42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF42" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AG42=""),"",ROUND(AVERAGE(C42:AE42),2))</f>
-        <v/>
-      </c>
-      <c r="AG42" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF42" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG42" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH42" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",IF(AJ42="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ42="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ42="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ42="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI42" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B43="",AJ42=""),"",ROUND(AVERAGE(C42:AH42),2))</f>
+        <v/>
+      </c>
+      <c r="AJ42" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G43="","",IF(UPPER(TRIM('Öğrenci Listesi'!G43))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G43))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G43))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G43))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G43))))),"")</f>
         <v/>
       </c>
@@ -6623,126 +7098,138 @@
         <v/>
       </c>
       <c r="C43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE43" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",IF(AG43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF43" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AG43=""),"",ROUND(AVERAGE(C43:AE43),2))</f>
-        <v/>
-      </c>
-      <c r="AG43" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF43" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG43" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH43" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",IF(AJ43="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ43="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ43="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ43="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI43" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B44="",AJ43=""),"",ROUND(AVERAGE(C43:AH43),2))</f>
+        <v/>
+      </c>
+      <c r="AJ43" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G44="","",IF(UPPER(TRIM('Öğrenci Listesi'!G44))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G44))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G44))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G44))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G44))))),"")</f>
         <v/>
       </c>
@@ -6757,133 +7244,145 @@
         <v/>
       </c>
       <c r="C44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="D44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="E44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="F44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="G44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="H44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="I44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="J44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="K44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="L44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="M44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="N44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="O44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="P44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Q44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="R44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="S44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="T44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="U44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="V44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="W44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="X44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Y44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="Z44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AA44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AB44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AC44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AD44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
         <v/>
       </c>
       <c r="AE44" s="16" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",IF(AG44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AG44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AG44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AG44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
-        <v/>
-      </c>
-      <c r="AF44" s="17" t="str">
-        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AG44=""),"",ROUND(AVERAGE(C44:AE44),2))</f>
-        <v/>
-      </c>
-      <c r="AG44" s="18" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AF44" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AG44" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AH44" s="16" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",IF(AJ44="Çok İyi",CHOOSE(RANDBETWEEN(1,5),4,4,4,4,3),IF(AJ44="İyi",CHOOSE(RANDBETWEEN(1,5),3,3,3,4,2),IF(AJ44="Yeterli",CHOOSE(RANDBETWEEN(1,5),2,2,2,3,1),IF(AJ44="Geliştirilmeli",CHOOSE(RANDBETWEEN(1,5),1,1,1,1,2),"")))))</f>
+        <v/>
+      </c>
+      <c r="AI44" s="17" t="str">
+        <f aca="false">IF(OR('Öğrenci Listesi'!B45="",AJ44=""),"",ROUND(AVERAGE(C44:AH44),2))</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="18" t="str">
         <f aca="false">IFERROR(IF('Öğrenci Listesi'!G45="","",IF(UPPER(TRIM('Öğrenci Listesi'!G45))="ÇOK İYİ","Çok İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G45))="İYİ","İyi",IF(UPPER(TRIM('Öğrenci Listesi'!G45))="YETERLİ","Yeterli",IF(UPPER(TRIM('Öğrenci Listesi'!G45))="GELİŞTİRİLMELİ","Geliştirilmeli",'Öğrenci Listesi'!G45))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -6917,6 +7416,9 @@
       <c r="AE45" s="19"/>
       <c r="AF45" s="19"/>
       <c r="AG45" s="19"/>
+      <c r="AH45" s="19"/>
+      <c r="AI45" s="19"/>
+      <c r="AJ45" s="19"/>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="str">
@@ -6938,11 +7440,11 @@
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
-      <c r="Q46" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
+      <c r="S46" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -6957,6 +7459,9 @@
       <c r="AE46" s="11"/>
       <c r="AF46" s="11"/>
       <c r="AG46" s="11"/>
+      <c r="AH46" s="11"/>
+      <c r="AI46" s="11"/>
+      <c r="AJ46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6979,12 +7484,12 @@
       <c r="N48" s="11"/>
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
-      <c r="Q48" s="11" t="n">
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11" t="n">
         <f aca="false">Bilgiler!B10</f>
         <v>0</v>
       </c>
-      <c r="R48" s="11"/>
-      <c r="S48" s="11"/>
       <c r="T48" s="11"/>
       <c r="U48" s="11"/>
       <c r="V48" s="11"/>
@@ -6999,18 +7504,21 @@
       <c r="AE48" s="11"/>
       <c r="AF48" s="11"/>
       <c r="AG48" s="11"/>
+      <c r="AH48" s="11"/>
+      <c r="AI48" s="11"/>
+      <c r="AJ48" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:AG2"/>
-    <mergeCell ref="A45:AG45"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="Q46:AG46"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="Q48:AG48"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A45:AJ45"/>
+    <mergeCell ref="A46:R46"/>
+    <mergeCell ref="S46:AJ46"/>
+    <mergeCell ref="A48:R48"/>
+    <mergeCell ref="S48:AJ48"/>
   </mergeCells>
-  <conditionalFormatting sqref="AG5:AG44">
+  <conditionalFormatting sqref="AJ5:AJ44">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Çok İyi"</formula>
     </cfRule>
@@ -7024,18 +7532,18 @@
       <formula>"Geliştirilmeli"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF5:AF44">
+  <conditionalFormatting sqref="AI5:AI44">
     <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>3</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(AF5&gt;=2,AF5&lt;3)</formula>
+      <formula>AND(AI5&gt;=2,AI5&lt;3)</formula>
     </cfRule>
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>AND(AF5&gt;=1.5,AF5&lt;2)</formula>
+      <formula>AND(AI5&gt;=1.5,AI5&lt;2)</formula>
     </cfRule>
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>AND(AF5&gt;0,AF5&lt;1.5)</formula>
+      <formula>AND(AI5&gt;0,AI5&lt;1.5)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
